--- a/raw/pnas.2217564120.sd01.xlsx
+++ b/raw/pnas.2217564120.sd01.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="839">
   <si>
     <t xml:space="preserve">Journal</t>
   </si>
@@ -2486,22 +2486,58 @@
     <t xml:space="preserve">0940-6360</t>
   </si>
   <si>
-    <t xml:space="preserve">Ecological Entomology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0307-6946, 1365-2311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Environmental Entomology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0046-225X, 1938-2936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archives of Insect Biochemistry and Physiology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0739-4462, 1520-6327</t>
+    <t xml:space="preserve">CROP AND PASTURE SCIENCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1836-0947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1836-5795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CROP HEALTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2948-1945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CROP PROTECTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0261-2194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1873-6904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CROP SCIENCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0011-183X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1435-0653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOURNAL OF AGRONOMY AND CROP SCIENCE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0931-2250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1439-037X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOURNAL OF CROP IMPROVEMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1542-7528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1542-7536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE CROP JOURNAL</t>
   </si>
 </sst>
 </file>
@@ -2638,7 +2674,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2699,12 +2735,24 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2785,7 +2833,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Y1000"/>
-  <sheetFormatPr defaultColWidth="11.1328125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="33.69"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.5"/>
@@ -12423,10 +12471,16 @@
       <c r="Y222" s="3"/>
     </row>
     <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A223" s="3"/>
-      <c r="B223" s="3"/>
-      <c r="C223" s="3"/>
-      <c r="D223" s="3"/>
+      <c r="A223" s="17" t="s">
+        <v>821</v>
+      </c>
+      <c r="B223" s="17"/>
+      <c r="C223" s="17" t="s">
+        <v>822</v>
+      </c>
+      <c r="D223" s="18" t="s">
+        <v>823</v>
+      </c>
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
       <c r="G223" s="3"/>
@@ -12450,10 +12504,14 @@
       <c r="Y223" s="3"/>
     </row>
     <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A224" s="3"/>
-      <c r="B224" s="3"/>
-      <c r="C224" s="3"/>
-      <c r="D224" s="3"/>
+      <c r="A224" s="17" t="s">
+        <v>824</v>
+      </c>
+      <c r="B224" s="17"/>
+      <c r="C224" s="17" t="s">
+        <v>825</v>
+      </c>
+      <c r="D224" s="19"/>
       <c r="E224" s="3"/>
       <c r="F224" s="3"/>
       <c r="G224" s="3"/>
@@ -12477,10 +12535,16 @@
       <c r="Y224" s="3"/>
     </row>
     <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A225" s="3"/>
-      <c r="B225" s="3"/>
-      <c r="C225" s="3"/>
-      <c r="D225" s="3"/>
+      <c r="A225" s="17" t="s">
+        <v>826</v>
+      </c>
+      <c r="B225" s="17"/>
+      <c r="C225" s="17" t="s">
+        <v>827</v>
+      </c>
+      <c r="D225" s="18" t="s">
+        <v>828</v>
+      </c>
       <c r="E225" s="3"/>
       <c r="F225" s="3"/>
       <c r="G225" s="3"/>
@@ -12504,10 +12568,16 @@
       <c r="Y225" s="3"/>
     </row>
     <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A226" s="3"/>
-      <c r="B226" s="3"/>
-      <c r="C226" s="3"/>
-      <c r="D226" s="3"/>
+      <c r="A226" s="17" t="s">
+        <v>829</v>
+      </c>
+      <c r="B226" s="17"/>
+      <c r="C226" s="17" t="s">
+        <v>830</v>
+      </c>
+      <c r="D226" s="18" t="s">
+        <v>831</v>
+      </c>
       <c r="E226" s="3"/>
       <c r="F226" s="3"/>
       <c r="G226" s="3"/>
@@ -12531,10 +12601,16 @@
       <c r="Y226" s="3"/>
     </row>
     <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A227" s="3"/>
-      <c r="B227" s="3"/>
-      <c r="C227" s="3"/>
-      <c r="D227" s="3"/>
+      <c r="A227" s="17" t="s">
+        <v>832</v>
+      </c>
+      <c r="B227" s="17"/>
+      <c r="C227" s="17" t="s">
+        <v>833</v>
+      </c>
+      <c r="D227" s="18" t="s">
+        <v>834</v>
+      </c>
       <c r="E227" s="3"/>
       <c r="F227" s="3"/>
       <c r="G227" s="3"/>
@@ -12558,10 +12634,16 @@
       <c r="Y227" s="3"/>
     </row>
     <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A228" s="3"/>
-      <c r="B228" s="3"/>
-      <c r="C228" s="3"/>
-      <c r="D228" s="3"/>
+      <c r="A228" s="17" t="s">
+        <v>835</v>
+      </c>
+      <c r="B228" s="17"/>
+      <c r="C228" s="17" t="s">
+        <v>836</v>
+      </c>
+      <c r="D228" s="18" t="s">
+        <v>837</v>
+      </c>
       <c r="E228" s="3"/>
       <c r="F228" s="3"/>
       <c r="G228" s="3"/>
@@ -12585,10 +12667,16 @@
       <c r="Y228" s="3"/>
     </row>
     <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A229" s="3"/>
-      <c r="B229" s="3"/>
-      <c r="C229" s="3"/>
-      <c r="D229" s="3"/>
+      <c r="A229" s="17" t="s">
+        <v>838</v>
+      </c>
+      <c r="B229" s="17"/>
+      <c r="C229" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D229" s="18" t="s">
+        <v>170</v>
+      </c>
       <c r="E229" s="3"/>
       <c r="F229" s="3"/>
       <c r="G229" s="3"/>
@@ -33444,43 +33532,93 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="10.484375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="10.4765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="19" width="41.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="19" width="14.13"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="4" style="19" width="10.48"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="17" t="s">
         <v>821</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+      <c r="D1" s="18" t="s">
         <v>823</v>
       </c>
-      <c r="B2" s="16" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17" t="s">
         <v>825</v>
       </c>
-      <c r="B3" s="16" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>825</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>826</v>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17" t="s">
+        <v>827</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="s">
+        <v>829</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17" t="s">
+        <v>830</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
+        <v>832</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17" t="s">
+        <v>833</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
+        <v>835</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17" t="s">
+        <v>836</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
+        <v>838</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
